--- a/employment_forms/032_hospitality_application_form--employment_forms.xlsx
+++ b/employment_forms/032_hospitality_application_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>communication_skills</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Communication Skills</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>communication_skills</t>
+          <t>conflict_resolution</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Communication Skills</t>
+          <t>Conflict Resolution</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>conflict_resolution</t>
+          <t>interpersonal_skills</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Conflict Resolution</t>
+          <t>Interpersonal Skills</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>interpersonal_skills</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Interpersonal Skills</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>job_opening_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>adaptability</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Adaptability</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>event_space</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Event Space</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>event_space</t>
+          <t>hospitality_industry</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Event Space</t>
+          <t>Hospitality Industry</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hospitality_industry</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hospitality Industry</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_opening_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>employed</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Employed</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>unemployed</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Unemployed</t>
+          <t>Self-Employed</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>self-employed</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Self-Employed</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>retired</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>employment_status_choices</t>
+          <t>available_commuting_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>On-Site</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>on-site</t>
+          <t>off-site</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>On-Site</t>
+          <t>Off-Site</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>off-site</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Off-Site</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>available_commuting_choices</t>
+          <t>available_language_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1624,27 +1624,10 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>Chinese</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>available_language_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
